--- a/output/Data and Chart Outputs/china_nbs_cpi_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_cpi_monthly.xlsx
@@ -158,7 +158,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China CPI headline y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China CPI headline y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$165</f>
+              <f>'Chart'!$B$2:$B$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -230,12 +230,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$165</f>
+              <f>'Chart'!$C$2:$C$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -266,12 +266,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$165</f>
+              <f>'Chart'!$D$2:$D$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -302,12 +302,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$165</f>
+              <f>'Chart'!$E$2:$E$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -338,12 +338,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$165</f>
+              <f>'Chart'!$F$2:$F$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$165</f>
+              <f>'Chart'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$165</f>
+              <f>'Chart'!$G$2:$G$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -479,7 +479,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China CPI energy-related items y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China CPI energy-related items y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -515,12 +515,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$A$2:$A$165</f>
+              <f>'Chart - CPI energy-related item'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$B$2:$B$165</f>
+              <f>'Chart - CPI energy-related item'!$B$2:$B$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -551,12 +551,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$A$2:$A$165</f>
+              <f>'Chart - CPI energy-related item'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$C$2:$C$165</f>
+              <f>'Chart - CPI energy-related item'!$C$2:$C$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -587,12 +587,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$A$2:$A$165</f>
+              <f>'Chart - CPI energy-related item'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$D$2:$D$165</f>
+              <f>'Chart - CPI energy-related item'!$D$2:$D$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -623,12 +623,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$A$2:$A$165</f>
+              <f>'Chart - CPI energy-related item'!$A$2:$A$166</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - CPI energy-related item'!$E$2:$E$165</f>
+              <f>'Chart - CPI energy-related item'!$E$2:$E$166</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1126,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4926,6 +4926,29 @@
         <v>0.8</v>
       </c>
       <c r="G165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G166" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4941,7 +4964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7256,6 +7279,23 @@
       </c>
       <c r="E165" t="n">
         <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D166" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E166" t="n">
+        <v>14.9</v>
       </c>
     </row>
   </sheetData>
@@ -7270,7 +7310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI165"/>
+  <dimension ref="A1:EI166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65689,6 +65729,425 @@
       </c>
       <c r="EI165" t="n">
         <v>10.3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>1</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S166" t="n">
+        <v>1</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BR166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BS166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BT166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BU166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BV166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BW166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BX166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY166" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="BZ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CB166" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="CC166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="CD166" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="CE166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CF166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CG166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CH166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CI166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="CJ166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CK166" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="CL166" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CM166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CN166" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CO166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CP166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ166" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="CR166" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS166" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT166" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="CU166" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="CV166" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="CW166" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="CX166" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="CY166" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CZ166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DC166" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="DD166" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="DE166" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="DF166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DG166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DH166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DI166" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="DJ166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DK166" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DL166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM166" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="DN166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DO166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DP166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DQ166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DR166" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DS166" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="DT166" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DU166" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DV166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DW166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DX166" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DY166" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ166" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="EA166" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="EB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC166" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="ED166" t="n">
+        <v>4</v>
+      </c>
+      <c r="EE166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="EF166" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EG166" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="EH166" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="EI166" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
